--- a/tcc-documentacao/Planejamento/Requisitos/requisitos-denuncias-urbanas.xlsx
+++ b/tcc-documentacao/Planejamento/Requisitos/requisitos-denuncias-urbanas.xlsx
@@ -1,31 +1,51 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alunoinfo.DESKTOP-FFTGG6Q\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{215F7403-69C2-4A38-969A-A1C9526DB101}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3B6D93E-41DC-44CA-9A90-9FAD7705FB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{352A2108-1EAB-4B7E-8DF7-D5280156B846}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="179021"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$2:$C$2</definedName>
+  </definedNames>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="138">
+  <si>
+    <t>Requisitos Funcionais Site (Usuário e administrador)</t>
+  </si>
+  <si>
+    <t>Requisitos Funcionais APP (Usuário e administrador)</t>
+  </si>
   <si>
     <t>Código</t>
   </si>
@@ -39,319 +59,154 @@
     <t>RFU 001</t>
   </si>
   <si>
-    <t>Requisitos Funcionais Site (Usuário e administrador)</t>
-  </si>
-  <si>
     <t>Usuário - O sistema deve exibir uma pagina inicial com informaçoes resumidas sobre o aplicativo, incluindo nome, slogan e principais funcionalidades.</t>
   </si>
   <si>
+    <t>Obrigatório</t>
+  </si>
+  <si>
+    <t>Usuário — O aplicativo deve apresentar uma tela inicial com informações sobre a plataforma e suas principais funcionalidades.</t>
+  </si>
+  <si>
     <t xml:space="preserve"> RFU 002</t>
   </si>
   <si>
+    <t>Usuário -O sistema deve disponibilizar uma página com orientações sobre como utilizar a plataforma e realizar uma denúncia.</t>
+  </si>
+  <si>
+    <t>Usuário — O aplicativo deve permitir que o usuário crie uma conta informando nome, e-mail e senha.</t>
+  </si>
+  <si>
     <t>RFU 003</t>
   </si>
   <si>
+    <t>Usuário - O sistema deve apresentar uma seção com as principais funcionalidades da plataforma, acompanhadas de descrições e imagens ilustrativas.</t>
+  </si>
+  <si>
+    <t>Usuário — O aplicativo deve permitir que o usuário realize login utilizando e-mail e senha.</t>
+  </si>
+  <si>
     <t>RFU 004</t>
   </si>
   <si>
+    <t>Usuário - O sistema deve disponibilizar uma página contendo a política de privacidade e as informações relacionadas ao tratamento dos dados dos usuários.</t>
+  </si>
+  <si>
+    <t>Usuário — O aplicativo deve permitir que o usuário visualize e altere seus dados cadastrais.</t>
+  </si>
+  <si>
     <t>RFU 005</t>
   </si>
   <si>
+    <t>Usuário — O sistema deve permitir que o usuário se cadastre e crie uma conta de acesso, informando nome, e-mail e senha.</t>
+  </si>
+  <si>
+    <t>Usuário — O aplicativo deve permitir que o usuário faça login e logout com autenticação segura (e-mail e senha).</t>
+  </si>
+  <si>
     <t>RFU 006</t>
   </si>
   <si>
+    <t>Usuário — O sistema deve permitir que o usuário altere suas informações, como e-mail e senha.</t>
+  </si>
+  <si>
+    <t>Usuário — O aplicativo deve permitir que o usuário registre uma denúncia informando título, descrição e categoria do problema.</t>
+  </si>
+  <si>
     <t>RFU 007</t>
   </si>
   <si>
+    <t>Usuário — O sistema deve permitir que o usuário faça login e logout com autenticação segura (e-mail e senha).</t>
+  </si>
+  <si>
+    <t>Usuário — O aplicativo deve permitir que o usuário utilize o GPS do dispositivo para identificar automaticamente a localização da ocorrência.</t>
+  </si>
+  <si>
     <t>RFU 008</t>
   </si>
   <si>
+    <t>Usuário — O sistema deve disponibilizar uma página "Sobre nós", com informações sobre a plataforma e seus objetivos.</t>
+  </si>
+  <si>
+    <t>Usuário — O aplicativo deve permitir que o usuário capture fotos da ocorrência utilizando a câmera do dispositivo.</t>
+  </si>
+  <si>
     <t>RFU 009</t>
   </si>
   <si>
+    <t>Usuário — O sistema deve disponibilizar um canal de "Fale Conosco", onde o usuário possa enviar dúvidas ou sugestões por formulário.</t>
+  </si>
+  <si>
+    <t>Usuário — O aplicativo deve permitir que o usuário anexe imagens e vídeos armazenados no dispositivo à denúncia.</t>
+  </si>
+  <si>
     <t>RFU 010</t>
   </si>
   <si>
+    <t>Usuário — O sistema deve permitir que o usuário registre uma nova denúncia, informando título, descrição do problema, categoria, endereço ou localização e data do registro.</t>
+  </si>
+  <si>
+    <t>Usuário — O aplicativo deve permitir que o usuário registre uma denúncia de forma anônima, sem a necessidade de informar seus dados pessoais.</t>
+  </si>
+  <si>
     <t>RFU 011</t>
   </si>
   <si>
+    <t>Usuário —  O sistema deve permitir que o usuário anexe arquivos como foto ou video.</t>
+  </si>
+  <si>
+    <t>Usuário — O aplicativo deve permitir que o usuário acompanhe o status das denúncias realizadas.</t>
+  </si>
+  <si>
     <t>RFU 012</t>
   </si>
   <si>
+    <t>Usuário —O sistema deve permitir o usuário informar a localização.</t>
+  </si>
+  <si>
+    <t>Usuário — O aplicativo deve enviar notificações ao usuário sobre alterações no status de suas denúncias.</t>
+  </si>
+  <si>
     <t>RFU 013</t>
   </si>
   <si>
+    <t>Usuário — O sistema deve identificar o órgão responsável e encaminhar a denúncia ao órgão competente.</t>
+  </si>
+  <si>
+    <t>Usuário — O aplicativo deve permitir que o usuário consulte o histórico de denúncias realizadas.</t>
+  </si>
+  <si>
     <t>RFU 014</t>
   </si>
   <si>
+    <t xml:space="preserve">Usuário — </t>
+  </si>
+  <si>
+    <t>Desejavel</t>
+  </si>
+  <si>
     <t>RFU 015</t>
   </si>
   <si>
+    <t>Usuário — O sistema deve permitir que o usuário registre uma denúncia de forma anônima, sem a necessidade de informar seus dados pessoais.</t>
+  </si>
+  <si>
     <t>RFU 016</t>
   </si>
   <si>
+    <t>Usuário — O sistema deve permitir que o usuário acompanhe o status de uma denúncia anônima por meio de um código de acompanhamento, sem revelar sua identidade.</t>
+  </si>
+  <si>
+    <t>Usuário —</t>
+  </si>
+  <si>
     <t>RFU 017</t>
   </si>
   <si>
+    <t>Usuário — O sistema poderá permitir que o usuário personalize o tema da interface, escolhendo entre modo claro e modo escuro.</t>
+  </si>
+  <si>
     <t>RFU 018</t>
-  </si>
-  <si>
-    <t>RFU 019</t>
-  </si>
-  <si>
-    <t>RFU 020</t>
-  </si>
-  <si>
-    <t>RFU 021</t>
-  </si>
-  <si>
-    <t>RFU 022</t>
-  </si>
-  <si>
-    <t>RFU 023</t>
-  </si>
-  <si>
-    <t>RFU 024</t>
-  </si>
-  <si>
-    <t>RFU 025</t>
-  </si>
-  <si>
-    <t>RFU 026</t>
-  </si>
-  <si>
-    <t>RFU 027</t>
-  </si>
-  <si>
-    <t>RFU 028</t>
-  </si>
-  <si>
-    <t>RFU 029</t>
-  </si>
-  <si>
-    <t>RFU 030</t>
-  </si>
-  <si>
-    <t>RFU 031</t>
-  </si>
-  <si>
-    <t>RFU 032</t>
-  </si>
-  <si>
-    <t>RFU 033</t>
-  </si>
-  <si>
-    <t>RFU 034</t>
-  </si>
-  <si>
-    <t>RFU 035</t>
-  </si>
-  <si>
-    <t>RFU 036</t>
-  </si>
-  <si>
-    <t>RFU 037</t>
-  </si>
-  <si>
-    <t>RFU 038</t>
-  </si>
-  <si>
-    <t>RFU 039</t>
-  </si>
-  <si>
-    <t>RFU 040</t>
-  </si>
-  <si>
-    <t>RFU 041</t>
-  </si>
-  <si>
-    <t>RFU 042</t>
-  </si>
-  <si>
-    <t>RFU 043</t>
-  </si>
-  <si>
-    <t>RFU 044</t>
-  </si>
-  <si>
-    <t>RFU 045</t>
-  </si>
-  <si>
-    <t>RFU 046</t>
-  </si>
-  <si>
-    <t>RFU 047</t>
-  </si>
-  <si>
-    <t>RFU 048</t>
-  </si>
-  <si>
-    <t>RFU 049</t>
-  </si>
-  <si>
-    <t>RFU 050</t>
-  </si>
-  <si>
-    <t>RFU 051</t>
-  </si>
-  <si>
-    <t>RFU 052</t>
-  </si>
-  <si>
-    <t>RFU 053</t>
-  </si>
-  <si>
-    <t>RFU 054</t>
-  </si>
-  <si>
-    <t>RFU 055</t>
-  </si>
-  <si>
-    <t>RFU 056</t>
-  </si>
-  <si>
-    <t>RFU 057</t>
-  </si>
-  <si>
-    <t>RFU 058</t>
-  </si>
-  <si>
-    <t>RFU 059</t>
-  </si>
-  <si>
-    <t>RFU 060</t>
-  </si>
-  <si>
-    <t>RFU 061</t>
-  </si>
-  <si>
-    <t>RFU 062</t>
-  </si>
-  <si>
-    <t>RFU 063</t>
-  </si>
-  <si>
-    <t>RFU 064</t>
-  </si>
-  <si>
-    <t>RFU 065</t>
-  </si>
-  <si>
-    <t>RFU 066</t>
-  </si>
-  <si>
-    <t>RFU 067</t>
-  </si>
-  <si>
-    <t>RFU 068</t>
-  </si>
-  <si>
-    <t>RFU 069</t>
-  </si>
-  <si>
-    <t>RFU 070</t>
-  </si>
-  <si>
-    <t>RFU 071</t>
-  </si>
-  <si>
-    <t>RFU 072</t>
-  </si>
-  <si>
-    <t>RFU 073</t>
-  </si>
-  <si>
-    <t>RFU 074</t>
-  </si>
-  <si>
-    <t>RFU 075</t>
-  </si>
-  <si>
-    <t>RFU 076</t>
-  </si>
-  <si>
-    <t>RFU 077</t>
-  </si>
-  <si>
-    <t>RFU 078</t>
-  </si>
-  <si>
-    <t>RFU 079</t>
-  </si>
-  <si>
-    <t>RFU 080</t>
-  </si>
-  <si>
-    <t>RFU 081</t>
-  </si>
-  <si>
-    <t>RFU 082</t>
-  </si>
-  <si>
-    <t>RFU 083</t>
-  </si>
-  <si>
-    <t>RFU 084</t>
-  </si>
-  <si>
-    <t>RFU 085</t>
-  </si>
-  <si>
-    <t>RFU 086</t>
-  </si>
-  <si>
-    <t>Obrigatório</t>
-  </si>
-  <si>
-    <t>Usuário - O sistema deve apresentar uma seção com a lista das principais funcionalidades do app, com descrições e imagens ilustrativas.</t>
-  </si>
-  <si>
-    <t>Usuário - O sistema deve exibir uma pagina com a politica de privacidade referente ao  uso do aplicativo e do site.</t>
-  </si>
-  <si>
-    <t>Usuário — O sistema deve permitir que o usuário se cadastre e crie uma conta de acesso, informando nome, e-mail e senha.</t>
-  </si>
-  <si>
-    <t>Usuário — O sistema deve permitir que o usuário faça login e logout com autenticação segura (e-mail e senha).</t>
-  </si>
-  <si>
-    <t>Usuário — O sistema deve disponibilizar uma página "Sobre nós", com informações sobre a plataforma e seus objetivos.</t>
-  </si>
-  <si>
-    <t>Usuário — O sistema deve disponibilizar um canal de "Fale Conosco", onde o usuário possa enviar dúvidas ou sugestões por formulário.</t>
-  </si>
-  <si>
-    <t>Usuário — O sistema poderá permitir que o usuário personalize o tema da interface, escolhendo entre modo claro e modo escuro.</t>
-  </si>
-  <si>
-    <t>Desejavel</t>
-  </si>
-  <si>
-    <t>RFU 087</t>
-  </si>
-  <si>
-    <t>Usuário — O sistema deve permitir que o usuário altere suas informações, como e-mail e senha.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Usuário — O sistema deve permitir que o usuário cadastre alimentos informando seus respectivos dados.  </t>
-  </si>
-  <si>
-    <t>Usuário — O sistema deve permitir que o usuário informe seus dados correspondentes a altura, peso, idade, biotipo e restrições alimentares.</t>
-  </si>
-  <si>
-    <t>Usuário — O sistema deve permitir o usuário a calcular o seu indice de massa corporal (IMC).</t>
-  </si>
-  <si>
-    <t>Usuário — O sistema deve sugerir ao usuário uma rotina de alimentação.</t>
-  </si>
-  <si>
-    <t>Usuário — O sistema deve ser capaz de estabelecer metas conforme os objetivos do usuário.</t>
-  </si>
-  <si>
-    <t>Usuário — O sistema deve exibir diariamente mensagens de incentivo ao usuário.</t>
-  </si>
-  <si>
-    <t>Usuário — O sistema deverá calcular as calorias consumidas pelo usuário.</t>
   </si>
   <si>
     <r>
@@ -368,56 +223,254 @@
     </r>
   </si>
   <si>
-    <t>Adm — O sistema deve permitir que o administrador edite as mensagens de incentivo.</t>
+    <t xml:space="preserve">Adm — </t>
+  </si>
+  <si>
+    <t>RFU 019</t>
+  </si>
+  <si>
+    <t>Adm — O sistema deve permitir que o administrador visualize todas as denúncias registradas pelos usuários.</t>
+  </si>
+  <si>
+    <t>RFU 020</t>
   </si>
   <si>
     <t xml:space="preserve"> Adm — O sistema deverá permitir que o administrador faça login, com e-mail e senha.</t>
   </si>
   <si>
-    <t>Adm — O sistema deve permitir  a visualização das mensagens recebidas pelo e fale conosco e possibilitar a resposta.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Adm —  O sistema deve permitir que o administrador visualize gráficos de uso da plataforma e metas cumpridas.</t>
-  </si>
-  <si>
-    <t>Requisitos Funcionais APP (Usuário e administrador)</t>
-  </si>
-  <si>
-    <t>Usuário - O sistema deve exibir uma tela inicial com informaçoes sobre o usuário, suas metas e progressos.</t>
-  </si>
-  <si>
-    <t>Usuário - O sistema deve exibir uma tela que contenha explicações sobre termos tecnicos da area da nutrição.</t>
-  </si>
-  <si>
-    <t>Usuário — O sistema deve permitir o usuário acessar o seu perfil, podendo fazer alterações, compartilhar e sequência de dias logados.</t>
-  </si>
-  <si>
-    <t>Usuário - O sistema deve exibir uma pagina que contenha explicações sobre uso do sistema.</t>
-  </si>
-  <si>
-    <t>Usuário — O sistema deve permitir que o usuário registre uma nova denúncia. Contendo título, descrição do problema, categoria, endereço, data do resgistro.</t>
-  </si>
-  <si>
-    <t>Usuário — O sistema deve permitir que o usuário anexe arquivos como foto ou video.</t>
-  </si>
-  <si>
-    <t>Usuário — O sistema deve permitir o usuário informar a localização.</t>
-  </si>
-  <si>
-    <t>Usuário — O sistema deve indentificar os órgão responsável pela solução do problema.</t>
-  </si>
-  <si>
-    <t>Usuário — O sistema deve ser capaz de encaminhar as denuncias para os órgão responsavel.</t>
-  </si>
-  <si>
-    <t>Usuário — O sistema deve enviar e-mails ao órgão responsavel.</t>
+    <t xml:space="preserve"> Adm —</t>
+  </si>
+  <si>
+    <t>RFU 021</t>
+  </si>
+  <si>
+    <t>Adm — O sistema deve permitir que o administrador filtre as denúncias por categoria, status, localização e período.</t>
+  </si>
+  <si>
+    <t>Adm —</t>
+  </si>
+  <si>
+    <t>RFU 022</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Adm —  O sistema deve permitir que o administrador atualize o status de uma denúncia conforme seu andamento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Adm —  </t>
+  </si>
+  <si>
+    <t>RFU 023</t>
+  </si>
+  <si>
+    <t>Adm — O sistema deve permitir que o administrador encaminhe uma denúncia ao órgão responsável pela resolução do problema.</t>
+  </si>
+  <si>
+    <t>RFU 024</t>
+  </si>
+  <si>
+    <t>Adm — O sistema deve permitir que o administrador cadastre, edite e remova categorias de denúncias.</t>
+  </si>
+  <si>
+    <t>RFU 025</t>
+  </si>
+  <si>
+    <t>Adm — O sistema deve permitir que o administrador cadastre, edite e remova órgãos responsáveis pelo atendimento das denúncias.</t>
+  </si>
+  <si>
+    <t>RFU 026</t>
+  </si>
+  <si>
+    <t>Adm— O sistema deve apresentar um painel com informações sobre as denúncias, incluindo quantidade de denúncias recebidas, em análise, encaminhadas, em atendimento e resolvidas.</t>
+  </si>
+  <si>
+    <t>RFU 027</t>
+  </si>
+  <si>
+    <t>RFU 028</t>
+  </si>
+  <si>
+    <t>RFU 029</t>
+  </si>
+  <si>
+    <t>RFU 030</t>
+  </si>
+  <si>
+    <t>RFU 031</t>
+  </si>
+  <si>
+    <t>RFU 032</t>
+  </si>
+  <si>
+    <t>RFU 033</t>
+  </si>
+  <si>
+    <t>RFU 034</t>
+  </si>
+  <si>
+    <t>RFU 035</t>
+  </si>
+  <si>
+    <t>RFU 036</t>
+  </si>
+  <si>
+    <t>RFU 037</t>
+  </si>
+  <si>
+    <t>RFU 038</t>
+  </si>
+  <si>
+    <t>RFU 039</t>
+  </si>
+  <si>
+    <t>RFU 040</t>
+  </si>
+  <si>
+    <t>RFU 041</t>
+  </si>
+  <si>
+    <t>RFU 042</t>
+  </si>
+  <si>
+    <t>RFU 043</t>
+  </si>
+  <si>
+    <t>RFU 044</t>
+  </si>
+  <si>
+    <t>RFU 045</t>
+  </si>
+  <si>
+    <t>RFU 046</t>
+  </si>
+  <si>
+    <t>RFU 047</t>
+  </si>
+  <si>
+    <t>RFU 048</t>
+  </si>
+  <si>
+    <t>RFU 049</t>
+  </si>
+  <si>
+    <t>RFU 050</t>
+  </si>
+  <si>
+    <t>RFU 051</t>
+  </si>
+  <si>
+    <t>RFU 052</t>
+  </si>
+  <si>
+    <t>RFU 053</t>
+  </si>
+  <si>
+    <t>RFU 054</t>
+  </si>
+  <si>
+    <t>RFU 055</t>
+  </si>
+  <si>
+    <t>RFU 056</t>
+  </si>
+  <si>
+    <t>RFU 057</t>
+  </si>
+  <si>
+    <t>RFU 058</t>
+  </si>
+  <si>
+    <t>RFU 059</t>
+  </si>
+  <si>
+    <t>RFU 060</t>
+  </si>
+  <si>
+    <t>RFU 061</t>
+  </si>
+  <si>
+    <t>RFU 062</t>
+  </si>
+  <si>
+    <t>RFU 063</t>
+  </si>
+  <si>
+    <t>RFU 064</t>
+  </si>
+  <si>
+    <t>RFU 065</t>
+  </si>
+  <si>
+    <t>RFU 066</t>
+  </si>
+  <si>
+    <t>RFU 067</t>
+  </si>
+  <si>
+    <t>RFU 068</t>
+  </si>
+  <si>
+    <t>RFU 069</t>
+  </si>
+  <si>
+    <t>RFU 070</t>
+  </si>
+  <si>
+    <t>RFU 071</t>
+  </si>
+  <si>
+    <t>RFU 072</t>
+  </si>
+  <si>
+    <t>RFU 073</t>
+  </si>
+  <si>
+    <t>RFU 074</t>
+  </si>
+  <si>
+    <t>RFU 075</t>
+  </si>
+  <si>
+    <t>RFU 076</t>
+  </si>
+  <si>
+    <t>RFU 077</t>
+  </si>
+  <si>
+    <t>RFU 078</t>
+  </si>
+  <si>
+    <t>RFU 079</t>
+  </si>
+  <si>
+    <t>RFU 080</t>
+  </si>
+  <si>
+    <t>RFU 081</t>
+  </si>
+  <si>
+    <t>RFU 082</t>
+  </si>
+  <si>
+    <t>RFU 083</t>
+  </si>
+  <si>
+    <t>RFU 084</t>
+  </si>
+  <si>
+    <t>RFU 085</t>
+  </si>
+  <si>
+    <t>RFU 086</t>
+  </si>
+  <si>
+    <t>RFU 087</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -451,6 +504,11 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="3">
@@ -531,7 +589,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -556,6 +614,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -584,7 +645,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -881,954 +942,971 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{824C14D4-FCA1-45E7-9429-E52589449756}">
   <dimension ref="A1:H95"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="17.26953125" customWidth="1"/>
-    <col min="2" max="2" width="35.1796875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="20.26953125" customWidth="1"/>
-    <col min="6" max="6" width="16.6328125" customWidth="1"/>
-    <col min="7" max="7" width="36.26953125" customWidth="1"/>
-    <col min="8" max="8" width="20.36328125" customWidth="1"/>
+    <col min="1" max="1" width="17.28515625" customWidth="1"/>
+    <col min="2" max="2" width="35.140625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="20.28515625" customWidth="1"/>
+    <col min="6" max="6" width="16.5703125" customWidth="1"/>
+    <col min="7" max="7" width="36.28515625" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:8" ht="14.45" customHeight="1">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="12"/>
+      <c r="F1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="11"/>
+      <c r="H1" s="12"/>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="11"/>
-      <c r="F1" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="G1" s="10"/>
-      <c r="H1" s="11"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="G2" s="3" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="84.95" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>3</v>
-      </c>
       <c r="G3" s="4" t="s">
-        <v>115</v>
+        <v>8</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="84.95" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>118</v>
+        <v>10</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>116</v>
+        <v>11</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="84.95" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>92</v>
+        <v>13</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>117</v>
+        <v>14</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="91.5">
       <c r="A6" s="6" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>93</v>
+        <v>17</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="84.95" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="84.95" customHeight="1">
       <c r="A8" s="6" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>101</v>
+        <v>22</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>101</v>
+        <v>23</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="84.95" customHeight="1">
       <c r="A9" s="6" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>95</v>
+        <v>26</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="84.95" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>96</v>
+        <v>29</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="84.95" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>97</v>
+        <v>31</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>97</v>
+        <v>32</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="91.5">
       <c r="A12" s="6" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>98</v>
+        <v>34</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>99</v>
+        <v>7</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="45.75">
       <c r="A13" s="6" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>119</v>
+        <v>37</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="84.95" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>103</v>
+        <v>41</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="84.95" customHeight="1">
       <c r="A15" s="6" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>121</v>
+        <v>43</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="84.95" customHeight="1">
       <c r="A16" s="6" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>122</v>
+        <v>43</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>105</v>
+        <v>46</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="84.95" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="91.5">
       <c r="A18" s="6" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>124</v>
+        <v>51</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>107</v>
+        <v>52</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="84.95" customHeight="1">
       <c r="A19" s="6" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>108</v>
+        <v>54</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>108</v>
+        <v>46</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="84.95" customHeight="1">
       <c r="A20" s="6" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>109</v>
+        <v>56</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>109</v>
+        <v>55</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>57</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="84.95" customHeight="1">
       <c r="A21" s="6" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>110</v>
+        <v>59</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>110</v>
+        <v>57</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="84.95" customHeight="1">
       <c r="A22" s="6" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>111</v>
+        <v>61</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>111</v>
+        <v>62</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="84.95" customHeight="1">
       <c r="A23" s="6" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="84.95" customHeight="1">
       <c r="A24" s="6" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>113</v>
+        <v>67</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>99</v>
+        <v>7</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="84.95" customHeight="1">
       <c r="A25" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="2"/>
-    </row>
-    <row r="26" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="84.95" customHeight="1">
       <c r="A26" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="2"/>
-    </row>
-    <row r="27" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+        <v>71</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="84.95" customHeight="1">
       <c r="A27" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="2"/>
-    </row>
-    <row r="28" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+        <v>73</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="107.25">
       <c r="A28" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="2"/>
-    </row>
-    <row r="29" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+        <v>75</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="84.95" customHeight="1">
       <c r="A29" s="6" t="s">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" ht="84.95" customHeight="1">
       <c r="A30" s="6" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" ht="84.95" customHeight="1">
       <c r="A31" s="6" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" ht="84.95" customHeight="1">
       <c r="A32" s="6" t="s">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="2"/>
     </row>
-    <row r="33" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" ht="84.95" customHeight="1">
       <c r="A33" s="6" t="s">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="2"/>
     </row>
-    <row r="34" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" ht="84.95" customHeight="1">
       <c r="A34" s="6" t="s">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="2"/>
     </row>
-    <row r="35" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" ht="84.95" customHeight="1">
       <c r="A35" s="6" t="s">
-        <v>37</v>
+        <v>83</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="2"/>
     </row>
-    <row r="36" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" ht="84.95" customHeight="1">
       <c r="A36" s="6" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="2"/>
     </row>
-    <row r="37" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" ht="84.95" customHeight="1">
       <c r="A37" s="6" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="2"/>
     </row>
-    <row r="38" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" ht="84.95" customHeight="1">
       <c r="A38" s="6" t="s">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="2"/>
     </row>
-    <row r="39" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" ht="84.95" customHeight="1">
       <c r="A39" s="6" t="s">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="2"/>
     </row>
-    <row r="40" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" ht="84.95" customHeight="1">
       <c r="A40" s="6" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="2"/>
     </row>
-    <row r="41" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" ht="84.95" customHeight="1">
       <c r="A41" s="6" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="2"/>
     </row>
-    <row r="42" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" ht="84.95" customHeight="1">
       <c r="A42" s="6" t="s">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="2"/>
     </row>
-    <row r="43" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" ht="84.95" customHeight="1">
       <c r="A43" s="6" t="s">
-        <v>45</v>
+        <v>91</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="2"/>
     </row>
-    <row r="44" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" ht="84.95" customHeight="1">
       <c r="A44" s="6" t="s">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="2"/>
     </row>
-    <row r="45" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" ht="84.95" customHeight="1">
       <c r="A45" s="6" t="s">
-        <v>47</v>
+        <v>93</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="2"/>
     </row>
-    <row r="46" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" ht="84.95" customHeight="1">
       <c r="A46" s="6" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="2"/>
     </row>
-    <row r="47" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" ht="84.95" customHeight="1">
       <c r="A47" s="6" t="s">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="2"/>
     </row>
-    <row r="48" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" ht="84.95" customHeight="1">
       <c r="A48" s="6" t="s">
-        <v>50</v>
+        <v>96</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="2"/>
     </row>
-    <row r="49" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" ht="84.95" customHeight="1">
       <c r="A49" s="6" t="s">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="2"/>
     </row>
-    <row r="50" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:3" ht="84.95" customHeight="1">
       <c r="A50" s="6" t="s">
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="2"/>
     </row>
-    <row r="51" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:3" ht="84.95" customHeight="1">
       <c r="A51" s="6" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="2"/>
     </row>
-    <row r="52" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:3" ht="84.95" customHeight="1">
       <c r="A52" s="6" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="2"/>
     </row>
-    <row r="53" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:3" ht="84.95" customHeight="1">
       <c r="A53" s="6" t="s">
-        <v>55</v>
+        <v>101</v>
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="2"/>
     </row>
-    <row r="54" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:3" ht="84.95" customHeight="1">
       <c r="A54" s="6" t="s">
-        <v>56</v>
+        <v>102</v>
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="2"/>
     </row>
-    <row r="55" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:3" ht="84.95" customHeight="1">
       <c r="A55" s="6" t="s">
-        <v>57</v>
+        <v>103</v>
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="2"/>
     </row>
-    <row r="56" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:3" ht="84.95" customHeight="1">
       <c r="A56" s="6" t="s">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="2"/>
     </row>
-    <row r="57" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:3" ht="84.95" customHeight="1">
       <c r="A57" s="6" t="s">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="2"/>
     </row>
-    <row r="58" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:3" ht="84.95" customHeight="1">
       <c r="A58" s="6" t="s">
-        <v>60</v>
+        <v>106</v>
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="2"/>
     </row>
-    <row r="59" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:3" ht="84.95" customHeight="1">
       <c r="A59" s="6" t="s">
-        <v>61</v>
+        <v>107</v>
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="2"/>
     </row>
-    <row r="60" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:3" ht="84.95" customHeight="1">
       <c r="A60" s="6" t="s">
-        <v>62</v>
+        <v>108</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="2"/>
     </row>
-    <row r="61" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:3" ht="84.95" customHeight="1">
       <c r="A61" s="6" t="s">
-        <v>63</v>
+        <v>109</v>
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="2"/>
     </row>
-    <row r="62" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:3" ht="84.95" customHeight="1">
       <c r="A62" s="6" t="s">
-        <v>64</v>
+        <v>110</v>
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="2"/>
     </row>
-    <row r="63" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:3" ht="84.95" customHeight="1">
       <c r="A63" s="6" t="s">
-        <v>65</v>
+        <v>111</v>
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="2"/>
     </row>
-    <row r="64" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:3" ht="84.95" customHeight="1">
       <c r="A64" s="6" t="s">
-        <v>66</v>
+        <v>112</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="2"/>
     </row>
-    <row r="65" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:3" ht="84.95" customHeight="1">
       <c r="A65" s="6" t="s">
-        <v>67</v>
+        <v>113</v>
       </c>
       <c r="B65" s="4"/>
       <c r="C65" s="2"/>
     </row>
-    <row r="66" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:3" ht="84.95" customHeight="1">
       <c r="A66" s="6" t="s">
-        <v>68</v>
+        <v>114</v>
       </c>
       <c r="B66" s="4"/>
       <c r="C66" s="2"/>
     </row>
-    <row r="67" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:3" ht="84.95" customHeight="1">
       <c r="A67" s="6" t="s">
-        <v>69</v>
+        <v>115</v>
       </c>
       <c r="B67" s="4"/>
       <c r="C67" s="2"/>
     </row>
-    <row r="68" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:3" ht="84.95" customHeight="1">
       <c r="A68" s="6" t="s">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="2"/>
     </row>
-    <row r="69" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:3" ht="84.95" customHeight="1">
       <c r="A69" s="6" t="s">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="2"/>
     </row>
-    <row r="70" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:3" ht="84.95" customHeight="1">
       <c r="A70" s="6" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="2"/>
     </row>
-    <row r="71" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:3" ht="84.95" customHeight="1">
       <c r="A71" s="6" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="B71" s="4"/>
       <c r="C71" s="2"/>
     </row>
-    <row r="72" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:3" ht="84.95" customHeight="1">
       <c r="A72" s="6" t="s">
-        <v>74</v>
+        <v>120</v>
       </c>
       <c r="B72" s="4"/>
       <c r="C72" s="2"/>
     </row>
-    <row r="73" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:3" ht="84.95" customHeight="1">
       <c r="A73" s="6" t="s">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="B73" s="4"/>
       <c r="C73" s="2"/>
     </row>
-    <row r="74" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:3" ht="84.95" customHeight="1">
       <c r="A74" s="6" t="s">
-        <v>76</v>
+        <v>122</v>
       </c>
       <c r="B74" s="4"/>
       <c r="C74" s="2"/>
     </row>
-    <row r="75" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:3" ht="84.95" customHeight="1">
       <c r="A75" s="6" t="s">
-        <v>77</v>
+        <v>123</v>
       </c>
       <c r="B75" s="4"/>
       <c r="C75" s="2"/>
     </row>
-    <row r="76" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:3" ht="84.95" customHeight="1">
       <c r="A76" s="6" t="s">
-        <v>78</v>
+        <v>124</v>
       </c>
       <c r="B76" s="4"/>
       <c r="C76" s="2"/>
     </row>
-    <row r="77" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:3" ht="84.95" customHeight="1">
       <c r="A77" s="6" t="s">
-        <v>79</v>
+        <v>125</v>
       </c>
       <c r="B77" s="4"/>
       <c r="C77" s="2"/>
     </row>
-    <row r="78" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:3" ht="84.95" customHeight="1">
       <c r="A78" s="6" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="B78" s="4"/>
       <c r="C78" s="2"/>
     </row>
-    <row r="79" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:3" ht="84.95" customHeight="1">
       <c r="A79" s="6" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="B79" s="4"/>
       <c r="C79" s="2"/>
     </row>
-    <row r="80" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:3" ht="84.95" customHeight="1">
       <c r="A80" s="6" t="s">
-        <v>82</v>
+        <v>128</v>
       </c>
       <c r="B80" s="4"/>
       <c r="C80" s="2"/>
     </row>
-    <row r="81" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:3" ht="84.95" customHeight="1">
       <c r="A81" s="6" t="s">
-        <v>83</v>
+        <v>129</v>
       </c>
       <c r="B81" s="4"/>
       <c r="C81" s="2"/>
     </row>
-    <row r="82" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:3" ht="84.95" customHeight="1">
       <c r="A82" s="6" t="s">
-        <v>84</v>
+        <v>130</v>
       </c>
       <c r="B82" s="4"/>
       <c r="C82" s="2"/>
     </row>
-    <row r="83" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:3" ht="84.95" customHeight="1">
       <c r="A83" s="6" t="s">
-        <v>85</v>
+        <v>131</v>
       </c>
       <c r="B83" s="4"/>
       <c r="C83" s="2"/>
     </row>
-    <row r="84" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:3" ht="84.95" customHeight="1">
       <c r="A84" s="6" t="s">
-        <v>86</v>
+        <v>132</v>
       </c>
       <c r="B84" s="4"/>
       <c r="C84" s="2"/>
     </row>
-    <row r="85" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:3" ht="84.95" customHeight="1">
       <c r="A85" s="6" t="s">
-        <v>87</v>
+        <v>133</v>
       </c>
       <c r="B85" s="4"/>
       <c r="C85" s="2"/>
     </row>
-    <row r="86" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:3" ht="84.95" customHeight="1">
       <c r="A86" s="6" t="s">
-        <v>88</v>
+        <v>134</v>
       </c>
       <c r="B86" s="4"/>
       <c r="C86" s="2"/>
     </row>
-    <row r="87" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:3" ht="84.95" customHeight="1">
       <c r="A87" s="6" t="s">
-        <v>89</v>
+        <v>135</v>
       </c>
       <c r="B87" s="4"/>
       <c r="C87" s="2"/>
     </row>
-    <row r="88" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:3" ht="84.95" customHeight="1">
       <c r="A88" s="6" t="s">
-        <v>90</v>
+        <v>136</v>
       </c>
       <c r="B88" s="4"/>
       <c r="C88" s="2"/>
     </row>
-    <row r="89" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:3" ht="84.95" customHeight="1">
       <c r="A89" s="6" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="B89" s="4"/>
       <c r="C89" s="2"/>
     </row>
-    <row r="90" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:3" ht="84.95" customHeight="1">
       <c r="A90" s="2"/>
       <c r="B90" s="4"/>
       <c r="C90" s="2"/>
     </row>
-    <row r="91" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="92" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="93" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="94" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="95" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="91" spans="1:3" ht="84.95" customHeight="1"/>
+    <row r="92" spans="1:3" ht="84.95" customHeight="1"/>
+    <row r="93" spans="1:3" ht="84.95" customHeight="1"/>
+    <row r="94" spans="1:3" ht="84.95" customHeight="1"/>
+    <row r="95" spans="1:3" ht="84.95" customHeight="1"/>
   </sheetData>
+  <autoFilter ref="A2:C89" xr:uid="{824C14D4-FCA1-45E7-9429-E52589449756}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="F1:H1"/>

--- a/tcc-documentacao/Planejamento/Requisitos/requisitos-denuncias-urbanas.xlsx
+++ b/tcc-documentacao/Planejamento/Requisitos/requisitos-denuncias-urbanas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20399"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alunoinfo.DESKTOP-FFTGG6Q\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alunoinfo\Desktop\tcc\tcc-etec\tcc-documentacao\Planejamento\Requisitos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3B6D93E-41DC-44CA-9A90-9FAD7705FB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDDAAFAA-D4F8-4EA3-B810-87EAC8AC4DAE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{352A2108-1EAB-4B7E-8DF7-D5280156B846}"/>
   </bookViews>
@@ -23,17 +23,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -65,9 +54,6 @@
     <t>Obrigatório</t>
   </si>
   <si>
-    <t>Usuário — O aplicativo deve apresentar uma tela inicial com informações sobre a plataforma e suas principais funcionalidades.</t>
-  </si>
-  <si>
     <t xml:space="preserve"> RFU 002</t>
   </si>
   <si>
@@ -137,9 +123,6 @@
     <t>Usuário — O sistema deve disponibilizar um canal de "Fale Conosco", onde o usuário possa enviar dúvidas ou sugestões por formulário.</t>
   </si>
   <si>
-    <t>Usuário — O aplicativo deve permitir que o usuário anexe imagens e vídeos armazenados no dispositivo à denúncia.</t>
-  </si>
-  <si>
     <t>RFU 010</t>
   </si>
   <si>
@@ -152,9 +135,6 @@
     <t>RFU 011</t>
   </si>
   <si>
-    <t>Usuário —  O sistema deve permitir que o usuário anexe arquivos como foto ou video.</t>
-  </si>
-  <si>
     <t>Usuário — O aplicativo deve permitir que o usuário acompanhe o status das denúncias realizadas.</t>
   </si>
   <si>
@@ -209,13 +189,273 @@
     <t>RFU 018</t>
   </si>
   <si>
+    <t xml:space="preserve">Adm — </t>
+  </si>
+  <si>
+    <t>RFU 019</t>
+  </si>
+  <si>
+    <t>Adm — O sistema deve permitir que o administrador visualize todas as denúncias registradas pelos usuários.</t>
+  </si>
+  <si>
+    <t>RFU 020</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Adm — O sistema deverá permitir que o administrador faça login, com e-mail e senha.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Adm —</t>
+  </si>
+  <si>
+    <t>RFU 021</t>
+  </si>
+  <si>
+    <t>Adm — O sistema deve permitir que o administrador filtre as denúncias por categoria, status, localização e período.</t>
+  </si>
+  <si>
+    <t>Adm —</t>
+  </si>
+  <si>
+    <t>RFU 022</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Adm —  </t>
+  </si>
+  <si>
+    <t>RFU 023</t>
+  </si>
+  <si>
+    <t>Adm — O sistema deve permitir que o administrador encaminhe uma denúncia ao órgão responsável pela resolução do problema.</t>
+  </si>
+  <si>
+    <t>RFU 024</t>
+  </si>
+  <si>
+    <t>Adm — O sistema deve permitir que o administrador cadastre, edite e remova categorias de denúncias.</t>
+  </si>
+  <si>
+    <t>RFU 025</t>
+  </si>
+  <si>
+    <t>Adm — O sistema deve permitir que o administrador cadastre, edite e remova órgãos responsáveis pelo atendimento das denúncias.</t>
+  </si>
+  <si>
+    <t>RFU 026</t>
+  </si>
+  <si>
+    <t>Adm— O sistema deve apresentar um painel com informações sobre as denúncias, incluindo quantidade de denúncias recebidas, em análise, encaminhadas, em atendimento e resolvidas.</t>
+  </si>
+  <si>
+    <t>RFU 027</t>
+  </si>
+  <si>
+    <t>RFU 028</t>
+  </si>
+  <si>
+    <t>RFU 029</t>
+  </si>
+  <si>
+    <t>RFU 030</t>
+  </si>
+  <si>
+    <t>RFU 031</t>
+  </si>
+  <si>
+    <t>RFU 032</t>
+  </si>
+  <si>
+    <t>RFU 033</t>
+  </si>
+  <si>
+    <t>RFU 034</t>
+  </si>
+  <si>
+    <t>RFU 035</t>
+  </si>
+  <si>
+    <t>RFU 036</t>
+  </si>
+  <si>
+    <t>RFU 037</t>
+  </si>
+  <si>
+    <t>RFU 038</t>
+  </si>
+  <si>
+    <t>RFU 039</t>
+  </si>
+  <si>
+    <t>RFU 040</t>
+  </si>
+  <si>
+    <t>RFU 041</t>
+  </si>
+  <si>
+    <t>RFU 042</t>
+  </si>
+  <si>
+    <t>RFU 043</t>
+  </si>
+  <si>
+    <t>RFU 044</t>
+  </si>
+  <si>
+    <t>RFU 045</t>
+  </si>
+  <si>
+    <t>RFU 046</t>
+  </si>
+  <si>
+    <t>RFU 047</t>
+  </si>
+  <si>
+    <t>RFU 048</t>
+  </si>
+  <si>
+    <t>RFU 049</t>
+  </si>
+  <si>
+    <t>RFU 050</t>
+  </si>
+  <si>
+    <t>RFU 051</t>
+  </si>
+  <si>
+    <t>RFU 052</t>
+  </si>
+  <si>
+    <t>RFU 053</t>
+  </si>
+  <si>
+    <t>RFU 054</t>
+  </si>
+  <si>
+    <t>RFU 055</t>
+  </si>
+  <si>
+    <t>RFU 056</t>
+  </si>
+  <si>
+    <t>RFU 057</t>
+  </si>
+  <si>
+    <t>RFU 058</t>
+  </si>
+  <si>
+    <t>RFU 059</t>
+  </si>
+  <si>
+    <t>RFU 060</t>
+  </si>
+  <si>
+    <t>RFU 061</t>
+  </si>
+  <si>
+    <t>RFU 062</t>
+  </si>
+  <si>
+    <t>RFU 063</t>
+  </si>
+  <si>
+    <t>RFU 064</t>
+  </si>
+  <si>
+    <t>RFU 065</t>
+  </si>
+  <si>
+    <t>RFU 066</t>
+  </si>
+  <si>
+    <t>RFU 067</t>
+  </si>
+  <si>
+    <t>RFU 068</t>
+  </si>
+  <si>
+    <t>RFU 069</t>
+  </si>
+  <si>
+    <t>RFU 070</t>
+  </si>
+  <si>
+    <t>RFU 071</t>
+  </si>
+  <si>
+    <t>RFU 072</t>
+  </si>
+  <si>
+    <t>RFU 073</t>
+  </si>
+  <si>
+    <t>RFU 074</t>
+  </si>
+  <si>
+    <t>RFU 075</t>
+  </si>
+  <si>
+    <t>RFU 076</t>
+  </si>
+  <si>
+    <t>RFU 077</t>
+  </si>
+  <si>
+    <t>RFU 078</t>
+  </si>
+  <si>
+    <t>RFU 079</t>
+  </si>
+  <si>
+    <t>RFU 080</t>
+  </si>
+  <si>
+    <t>RFU 081</t>
+  </si>
+  <si>
+    <t>RFU 082</t>
+  </si>
+  <si>
+    <t>RFU 083</t>
+  </si>
+  <si>
+    <t>RFU 084</t>
+  </si>
+  <si>
+    <t>RFU 085</t>
+  </si>
+  <si>
+    <t>RFU 086</t>
+  </si>
+  <si>
+    <t>RFU 087</t>
+  </si>
+  <si>
     <r>
+      <t>Usuário —  O sistema deve permitir que o usuário anexe arquivos como foto ou</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> video.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">Adm — </t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -223,254 +463,20 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Adm — </t>
-  </si>
-  <si>
-    <t>RFU 019</t>
-  </si>
-  <si>
-    <t>Adm — O sistema deve permitir que o administrador visualize todas as denúncias registradas pelos usuários.</t>
-  </si>
-  <si>
-    <t>RFU 020</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Adm — O sistema deverá permitir que o administrador faça login, com e-mail e senha.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Adm —</t>
-  </si>
-  <si>
-    <t>RFU 021</t>
-  </si>
-  <si>
-    <t>Adm — O sistema deve permitir que o administrador filtre as denúncias por categoria, status, localização e período.</t>
-  </si>
-  <si>
-    <t>Adm —</t>
-  </si>
-  <si>
-    <t>RFU 022</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Adm —  O sistema deve permitir que o administrador atualize o status de uma denúncia conforme seu andamento.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Adm —  </t>
-  </si>
-  <si>
-    <t>RFU 023</t>
-  </si>
-  <si>
-    <t>Adm — O sistema deve permitir que o administrador encaminhe uma denúncia ao órgão responsável pela resolução do problema.</t>
-  </si>
-  <si>
-    <t>RFU 024</t>
-  </si>
-  <si>
-    <t>Adm — O sistema deve permitir que o administrador cadastre, edite e remova categorias de denúncias.</t>
-  </si>
-  <si>
-    <t>RFU 025</t>
-  </si>
-  <si>
-    <t>Adm — O sistema deve permitir que o administrador cadastre, edite e remova órgãos responsáveis pelo atendimento das denúncias.</t>
-  </si>
-  <si>
-    <t>RFU 026</t>
-  </si>
-  <si>
-    <t>Adm— O sistema deve apresentar um painel com informações sobre as denúncias, incluindo quantidade de denúncias recebidas, em análise, encaminhadas, em atendimento e resolvidas.</t>
-  </si>
-  <si>
-    <t>RFU 027</t>
-  </si>
-  <si>
-    <t>RFU 028</t>
-  </si>
-  <si>
-    <t>RFU 029</t>
-  </si>
-  <si>
-    <t>RFU 030</t>
-  </si>
-  <si>
-    <t>RFU 031</t>
-  </si>
-  <si>
-    <t>RFU 032</t>
-  </si>
-  <si>
-    <t>RFU 033</t>
-  </si>
-  <si>
-    <t>RFU 034</t>
-  </si>
-  <si>
-    <t>RFU 035</t>
-  </si>
-  <si>
-    <t>RFU 036</t>
-  </si>
-  <si>
-    <t>RFU 037</t>
-  </si>
-  <si>
-    <t>RFU 038</t>
-  </si>
-  <si>
-    <t>RFU 039</t>
-  </si>
-  <si>
-    <t>RFU 040</t>
-  </si>
-  <si>
-    <t>RFU 041</t>
-  </si>
-  <si>
-    <t>RFU 042</t>
-  </si>
-  <si>
-    <t>RFU 043</t>
-  </si>
-  <si>
-    <t>RFU 044</t>
-  </si>
-  <si>
-    <t>RFU 045</t>
-  </si>
-  <si>
-    <t>RFU 046</t>
-  </si>
-  <si>
-    <t>RFU 047</t>
-  </si>
-  <si>
-    <t>RFU 048</t>
-  </si>
-  <si>
-    <t>RFU 049</t>
-  </si>
-  <si>
-    <t>RFU 050</t>
-  </si>
-  <si>
-    <t>RFU 051</t>
-  </si>
-  <si>
-    <t>RFU 052</t>
-  </si>
-  <si>
-    <t>RFU 053</t>
-  </si>
-  <si>
-    <t>RFU 054</t>
-  </si>
-  <si>
-    <t>RFU 055</t>
-  </si>
-  <si>
-    <t>RFU 056</t>
-  </si>
-  <si>
-    <t>RFU 057</t>
-  </si>
-  <si>
-    <t>RFU 058</t>
-  </si>
-  <si>
-    <t>RFU 059</t>
-  </si>
-  <si>
-    <t>RFU 060</t>
-  </si>
-  <si>
-    <t>RFU 061</t>
-  </si>
-  <si>
-    <t>RFU 062</t>
-  </si>
-  <si>
-    <t>RFU 063</t>
-  </si>
-  <si>
-    <t>RFU 064</t>
-  </si>
-  <si>
-    <t>RFU 065</t>
-  </si>
-  <si>
-    <t>RFU 066</t>
-  </si>
-  <si>
-    <t>RFU 067</t>
-  </si>
-  <si>
-    <t>RFU 068</t>
-  </si>
-  <si>
-    <t>RFU 069</t>
-  </si>
-  <si>
-    <t>RFU 070</t>
-  </si>
-  <si>
-    <t>RFU 071</t>
-  </si>
-  <si>
-    <t>RFU 072</t>
-  </si>
-  <si>
-    <t>RFU 073</t>
-  </si>
-  <si>
-    <t>RFU 074</t>
-  </si>
-  <si>
-    <t>RFU 075</t>
-  </si>
-  <si>
-    <t>RFU 076</t>
-  </si>
-  <si>
-    <t>RFU 077</t>
-  </si>
-  <si>
-    <t>RFU 078</t>
-  </si>
-  <si>
-    <t>RFU 079</t>
-  </si>
-  <si>
-    <t>RFU 080</t>
-  </si>
-  <si>
-    <t>RFU 081</t>
-  </si>
-  <si>
-    <t>RFU 082</t>
-  </si>
-  <si>
-    <t>RFU 083</t>
-  </si>
-  <si>
-    <t>RFU 084</t>
-  </si>
-  <si>
-    <t>RFU 085</t>
-  </si>
-  <si>
-    <t>RFU 086</t>
-  </si>
-  <si>
-    <t>RFU 087</t>
+    <t xml:space="preserve"> Adm —  O sistema deve permitir que o administrador e o orgão responsavel atualize o status de uma denúncia conforme seu andamento.</t>
+  </si>
+  <si>
+    <t>Usuário — O aplicativo deve apresentar uma tela com informações sobre a plataforma e suas principais funcionalidades.</t>
+  </si>
+  <si>
+    <t>Usuário — O aplicativo deve permitir que o usuário anexe imagens  armazenados no dispositivo à denúncia.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -500,15 +506,21 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -589,7 +601,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -615,7 +627,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -626,6 +638,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -645,7 +660,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -942,7 +957,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{824C14D4-FCA1-45E7-9429-E52589449756}">
   <dimension ref="A1:H95"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.28515625" customWidth="1"/>
     <col min="2" max="2" width="35.140625" style="5" customWidth="1"/>
@@ -952,7 +967,7 @@
     <col min="8" max="8" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="14.45" customHeight="1">
+    <row r="1" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -964,7 +979,7 @@
       <c r="G1" s="11"/>
       <c r="H1" s="12"/>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -984,7 +999,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="84.95" customHeight="1">
+    <row r="3" spans="1:8" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
@@ -998,913 +1013,913 @@
         <v>5</v>
       </c>
       <c r="G3" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="84.95" customHeight="1">
-      <c r="A4" s="6" t="s">
+      <c r="B4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="84.95" customHeight="1">
-      <c r="A5" s="6" t="s">
+      <c r="B5" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="91.5">
-      <c r="A6" s="6" t="s">
+      <c r="B6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="C6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="84.95" customHeight="1">
-      <c r="A7" s="6" t="s">
+      <c r="B7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="C7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="4" t="s">
+      <c r="H7" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="84.95" customHeight="1">
-      <c r="A8" s="6" t="s">
+      <c r="B8" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="C8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" s="4" t="s">
+      <c r="H8" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="H8" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="84.95" customHeight="1">
-      <c r="A9" s="6" t="s">
+      <c r="B9" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" s="4" t="s">
+      <c r="H9" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="84.95" customHeight="1">
-      <c r="A10" s="6" t="s">
+      <c r="B10" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="C10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G10" s="4" t="s">
+      <c r="H10" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="H10" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="84.95" customHeight="1">
-      <c r="A11" s="6" t="s">
+      <c r="B11" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="C11" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G11" s="8" t="s">
+      <c r="B12" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H11" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="91.5">
-      <c r="A12" s="6" t="s">
+      <c r="C12" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="H12" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="G12" s="4" t="s">
+      <c r="B13" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="H12" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="45.75">
-      <c r="A13" s="6" t="s">
+      <c r="H13" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B14" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" s="6" t="s">
+      <c r="C14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G14" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="H13" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="84.95" customHeight="1">
-      <c r="A14" s="6" t="s">
+      <c r="H14" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B15" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" s="6" t="s">
+      <c r="C15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G15" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H14" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="84.95" customHeight="1">
-      <c r="A15" s="6" t="s">
+      <c r="H15" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B16" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G15" s="4" t="s">
+      <c r="H16" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="H15" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="84.95" customHeight="1">
-      <c r="A16" s="6" t="s">
+    </row>
+    <row r="17" spans="1:8" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B17" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H16" s="2" t="s">
+      <c r="H17" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" ht="84.95" customHeight="1">
-      <c r="A17" s="6" t="s">
+      <c r="B18" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="C18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="91.5">
-      <c r="A18" s="6" t="s">
+      <c r="H18" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B19" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" s="6" t="s">
+      <c r="C19" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F19" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G19" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="H18" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="84.95" customHeight="1">
-      <c r="A19" s="6" t="s">
+      <c r="B20" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="G20" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="H20" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F19" s="6" t="s">
+      <c r="B21" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G21" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="G19" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="84.95" customHeight="1">
-      <c r="A20" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" s="4" t="s">
+      <c r="H21" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="G20" s="9" t="s">
+      <c r="B22" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H20" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="84.95" customHeight="1">
-      <c r="A21" s="6" t="s">
+      <c r="C22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="G22" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="H22" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="84.95" customHeight="1">
-      <c r="A22" s="6" t="s">
+      <c r="B23" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="C23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G23" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="G22" s="4" t="s">
+      <c r="H23" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="H22" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="84.95" customHeight="1">
-      <c r="A23" s="6" t="s">
+      <c r="B24" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G24" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="H24" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G23" s="4" t="s">
+      <c r="B25" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="H23" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="84.95" customHeight="1">
-      <c r="A24" s="6" t="s">
+      <c r="C25" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B26" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="G24" s="4" t="s">
+      <c r="C26" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="H24" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="84.95" customHeight="1">
-      <c r="A25" s="6" t="s">
+      <c r="B27" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="C27" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="84.95" customHeight="1">
-      <c r="A26" s="6" t="s">
+      <c r="B28" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="C28" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
         <v>72</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="84.95" customHeight="1">
-      <c r="A27" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="107.25">
-      <c r="A28" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="84.95" customHeight="1">
-      <c r="A29" s="6" t="s">
-        <v>77</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:8" ht="84.95" customHeight="1">
+    <row r="30" spans="1:8" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:8" ht="84.95" customHeight="1">
+    <row r="31" spans="1:8" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:8" ht="84.95" customHeight="1">
+    <row r="32" spans="1:8" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="2"/>
     </row>
-    <row r="33" spans="1:3" ht="84.95" customHeight="1">
+    <row r="33" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="2"/>
     </row>
-    <row r="34" spans="1:3" ht="84.95" customHeight="1">
+    <row r="34" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="2"/>
     </row>
-    <row r="35" spans="1:3" ht="84.95" customHeight="1">
+    <row r="35" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="2"/>
     </row>
-    <row r="36" spans="1:3" ht="84.95" customHeight="1">
+    <row r="36" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="2"/>
     </row>
-    <row r="37" spans="1:3" ht="84.95" customHeight="1">
+    <row r="37" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="2"/>
     </row>
-    <row r="38" spans="1:3" ht="84.95" customHeight="1">
+    <row r="38" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="2"/>
     </row>
-    <row r="39" spans="1:3" ht="84.95" customHeight="1">
+    <row r="39" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="2"/>
     </row>
-    <row r="40" spans="1:3" ht="84.95" customHeight="1">
+    <row r="40" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="2"/>
     </row>
-    <row r="41" spans="1:3" ht="84.95" customHeight="1">
+    <row r="41" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="2"/>
     </row>
-    <row r="42" spans="1:3" ht="84.95" customHeight="1">
+    <row r="42" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="2"/>
     </row>
-    <row r="43" spans="1:3" ht="84.95" customHeight="1">
+    <row r="43" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="2"/>
     </row>
-    <row r="44" spans="1:3" ht="84.95" customHeight="1">
+    <row r="44" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="2"/>
     </row>
-    <row r="45" spans="1:3" ht="84.95" customHeight="1">
+    <row r="45" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="2"/>
     </row>
-    <row r="46" spans="1:3" ht="84.95" customHeight="1">
+    <row r="46" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="2"/>
     </row>
-    <row r="47" spans="1:3" ht="84.95" customHeight="1">
+    <row r="47" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="2"/>
     </row>
-    <row r="48" spans="1:3" ht="84.95" customHeight="1">
+    <row r="48" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="2"/>
     </row>
-    <row r="49" spans="1:3" ht="84.95" customHeight="1">
+    <row r="49" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="2"/>
     </row>
-    <row r="50" spans="1:3" ht="84.95" customHeight="1">
+    <row r="50" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="2"/>
     </row>
-    <row r="51" spans="1:3" ht="84.95" customHeight="1">
+    <row r="51" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="2"/>
     </row>
-    <row r="52" spans="1:3" ht="84.95" customHeight="1">
+    <row r="52" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="2"/>
     </row>
-    <row r="53" spans="1:3" ht="84.95" customHeight="1">
+    <row r="53" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="2"/>
     </row>
-    <row r="54" spans="1:3" ht="84.95" customHeight="1">
+    <row r="54" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="2"/>
     </row>
-    <row r="55" spans="1:3" ht="84.95" customHeight="1">
+    <row r="55" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="2"/>
     </row>
-    <row r="56" spans="1:3" ht="84.95" customHeight="1">
+    <row r="56" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="2"/>
     </row>
-    <row r="57" spans="1:3" ht="84.95" customHeight="1">
+    <row r="57" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="2"/>
     </row>
-    <row r="58" spans="1:3" ht="84.95" customHeight="1">
+    <row r="58" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="2"/>
     </row>
-    <row r="59" spans="1:3" ht="84.95" customHeight="1">
+    <row r="59" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="2"/>
     </row>
-    <row r="60" spans="1:3" ht="84.95" customHeight="1">
+    <row r="60" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="2"/>
     </row>
-    <row r="61" spans="1:3" ht="84.95" customHeight="1">
+    <row r="61" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="2"/>
     </row>
-    <row r="62" spans="1:3" ht="84.95" customHeight="1">
+    <row r="62" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="2"/>
     </row>
-    <row r="63" spans="1:3" ht="84.95" customHeight="1">
+    <row r="63" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="2"/>
     </row>
-    <row r="64" spans="1:3" ht="84.95" customHeight="1">
+    <row r="64" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="2"/>
     </row>
-    <row r="65" spans="1:3" ht="84.95" customHeight="1">
+    <row r="65" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B65" s="4"/>
       <c r="C65" s="2"/>
     </row>
-    <row r="66" spans="1:3" ht="84.95" customHeight="1">
+    <row r="66" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B66" s="4"/>
       <c r="C66" s="2"/>
     </row>
-    <row r="67" spans="1:3" ht="84.95" customHeight="1">
+    <row r="67" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B67" s="4"/>
       <c r="C67" s="2"/>
     </row>
-    <row r="68" spans="1:3" ht="84.95" customHeight="1">
+    <row r="68" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="2"/>
     </row>
-    <row r="69" spans="1:3" ht="84.95" customHeight="1">
+    <row r="69" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="2"/>
     </row>
-    <row r="70" spans="1:3" ht="84.95" customHeight="1">
+    <row r="70" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="2"/>
     </row>
-    <row r="71" spans="1:3" ht="84.95" customHeight="1">
+    <row r="71" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B71" s="4"/>
       <c r="C71" s="2"/>
     </row>
-    <row r="72" spans="1:3" ht="84.95" customHeight="1">
+    <row r="72" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B72" s="4"/>
       <c r="C72" s="2"/>
     </row>
-    <row r="73" spans="1:3" ht="84.95" customHeight="1">
+    <row r="73" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B73" s="4"/>
       <c r="C73" s="2"/>
     </row>
-    <row r="74" spans="1:3" ht="84.95" customHeight="1">
+    <row r="74" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B74" s="4"/>
       <c r="C74" s="2"/>
     </row>
-    <row r="75" spans="1:3" ht="84.95" customHeight="1">
+    <row r="75" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B75" s="4"/>
       <c r="C75" s="2"/>
     </row>
-    <row r="76" spans="1:3" ht="84.95" customHeight="1">
+    <row r="76" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B76" s="4"/>
       <c r="C76" s="2"/>
     </row>
-    <row r="77" spans="1:3" ht="84.95" customHeight="1">
+    <row r="77" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B77" s="4"/>
       <c r="C77" s="2"/>
     </row>
-    <row r="78" spans="1:3" ht="84.95" customHeight="1">
+    <row r="78" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B78" s="4"/>
       <c r="C78" s="2"/>
     </row>
-    <row r="79" spans="1:3" ht="84.95" customHeight="1">
+    <row r="79" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B79" s="4"/>
       <c r="C79" s="2"/>
     </row>
-    <row r="80" spans="1:3" ht="84.95" customHeight="1">
+    <row r="80" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B80" s="4"/>
       <c r="C80" s="2"/>
     </row>
-    <row r="81" spans="1:3" ht="84.95" customHeight="1">
+    <row r="81" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B81" s="4"/>
       <c r="C81" s="2"/>
     </row>
-    <row r="82" spans="1:3" ht="84.95" customHeight="1">
+    <row r="82" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B82" s="4"/>
       <c r="C82" s="2"/>
     </row>
-    <row r="83" spans="1:3" ht="84.95" customHeight="1">
+    <row r="83" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B83" s="4"/>
       <c r="C83" s="2"/>
     </row>
-    <row r="84" spans="1:3" ht="84.95" customHeight="1">
+    <row r="84" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B84" s="4"/>
       <c r="C84" s="2"/>
     </row>
-    <row r="85" spans="1:3" ht="84.95" customHeight="1">
+    <row r="85" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B85" s="4"/>
       <c r="C85" s="2"/>
     </row>
-    <row r="86" spans="1:3" ht="84.95" customHeight="1">
+    <row r="86" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B86" s="4"/>
       <c r="C86" s="2"/>
     </row>
-    <row r="87" spans="1:3" ht="84.95" customHeight="1">
+    <row r="87" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B87" s="4"/>
       <c r="C87" s="2"/>
     </row>
-    <row r="88" spans="1:3" ht="84.95" customHeight="1">
+    <row r="88" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B88" s="4"/>
       <c r="C88" s="2"/>
     </row>
-    <row r="89" spans="1:3" ht="84.95" customHeight="1">
+    <row r="89" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B89" s="4"/>
       <c r="C89" s="2"/>
     </row>
-    <row r="90" spans="1:3" ht="84.95" customHeight="1">
+    <row r="90" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
       <c r="B90" s="4"/>
       <c r="C90" s="2"/>
     </row>
-    <row r="91" spans="1:3" ht="84.95" customHeight="1"/>
-    <row r="92" spans="1:3" ht="84.95" customHeight="1"/>
-    <row r="93" spans="1:3" ht="84.95" customHeight="1"/>
-    <row r="94" spans="1:3" ht="84.95" customHeight="1"/>
-    <row r="95" spans="1:3" ht="84.95" customHeight="1"/>
+    <row r="91" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="1:3" ht="84.95" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="A2:C89" xr:uid="{824C14D4-FCA1-45E7-9429-E52589449756}"/>
   <mergeCells count="2">
